--- a/exports/registri_compilati/registro_1EB.xlsx
+++ b/exports/registri_compilati/registro_1EB.xlsx
@@ -53,7 +53,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,16 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,16 +134,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -703,9 +687,9 @@
           <t>FLORES CARVAJAL ALBERT ERIK</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -763,9 +747,9 @@
           <t>MERINO RODRIGUEZ MICHELE ALIPIO</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -775,9 +759,9 @@
           <t>MUSARDO MIRKO</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -787,9 +771,9 @@
           <t>NIANE KHADIM</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -811,9 +795,9 @@
           <t>RIGAMONTI ALESSANDRO</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -902,38 +886,38 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>ORA</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>20:18</t>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>00:18</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>DOCENTE</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>dirigente@itispaleocapa.it</t>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>ufficiotecnico@itispaleocapa.it</t>
         </is>
       </c>
     </row>
